--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -3914,13 +3914,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="O24" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2203687091711874</v>
+        <v>0.2350599564492666</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1950</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -3914,13 +3914,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O24" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2350599564492666</v>
+        <v>0.2387327682687863</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O16" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3525899346738999</v>
+        <v>0.3562627464934197</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3914,13 +3914,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O24" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2387327682687863</v>
+        <v>0.2350599564492666</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -3914,13 +3914,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O24" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2350599564492666</v>
+        <v>0.246078391907826</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1955</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -3914,13 +3914,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O24" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R24" t="n">
-        <v>0.246078391907826</v>
+        <v>0.2497512037273457</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O16" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3562627464934197</v>
+        <v>0.3599355583129394</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3914,13 +3914,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O24" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2497512037273457</v>
+        <v>0.2607696391859051</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1959</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3599355583129394</v>
+        <v>0.3636083701324592</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="R31" t="n">
-        <v>0.01101843545855937</v>
+        <v>0.2901521337420634</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1963</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -869,12 +869,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -899,29 +899,26 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>257</v>
-      </c>
-      <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9439126376165859</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -955,12 +952,12 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -975,12 +972,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1017,12 +1014,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1047,29 +1044,26 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="O4" t="n">
-        <v>270</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9916591912703433</v>
+        <v>0.2306777138223816</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1103,12 +1097,12 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1123,12 +1117,12 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1165,12 +1159,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1195,26 +1189,26 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>314</v>
+        <v>17</v>
       </c>
       <c r="O5" t="n">
-        <v>314</v>
+        <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.153262911329214</v>
+        <v>6.322076318617771</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1248,12 +1242,12 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1268,12 +1262,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -1310,12 +1304,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1340,26 +1334,26 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>259</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>259</v>
+        <v>48</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9512582612556257</v>
+        <v>0.8363154658599474</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1393,12 +1387,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1413,12 +1407,12 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -1455,12 +1449,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1485,26 +1479,26 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="O7" t="n">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6207051974988445</v>
+        <v>0.8868781679809853</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1538,12 +1532,12 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1558,12 +1552,12 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -1600,12 +1594,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1630,19 +1624,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1680,7 +1668,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1700,7 +1688,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -1742,12 +1730,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1772,23 +1760,26 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="O9" t="n">
-        <v>24</v>
+        <v>58</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8107102087005699</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1822,7 +1813,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1842,7 +1833,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -1884,12 +1875,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1914,23 +1905,26 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="O10" t="n">
-        <v>11</v>
+        <v>71</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.29311722479848</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1964,7 +1958,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1984,7 +1978,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2026,12 +2020,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2056,23 +2050,29 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="O11" t="n">
-        <v>97</v>
+        <v>257</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.9439126376165859</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2198,23 +2198,26 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2248,7 +2251,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -2268,7 +2271,7 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -2310,12 +2313,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2340,23 +2343,26 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3690843421158106</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2390,7 +2396,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2410,7 +2416,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -2452,12 +2458,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2482,23 +2488,26 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5.20641579180287</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2532,7 +2541,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2552,7 +2561,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -2594,12 +2603,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2624,23 +2633,26 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="O15" t="n">
-        <v>21</v>
+        <v>124</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.160481620138198</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2674,7 +2686,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2694,7 +2706,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -2736,12 +2748,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2766,26 +2778,26 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3636083701324592</v>
+        <v>0.3130158239932889</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2819,12 +2831,12 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2839,12 +2851,12 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -2881,12 +2893,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2911,19 +2923,13 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2961,7 +2967,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2981,7 +2987,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -3023,12 +3029,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3053,23 +3059,26 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4193328665692603</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3103,7 +3112,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -3123,7 +3132,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -3165,12 +3174,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3195,23 +3204,26 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="O19" t="n">
-        <v>7</v>
+        <v>58</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.873250690680448</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3245,7 +3257,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -3265,7 +3277,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -3307,12 +3319,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3337,23 +3349,29 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>48</v>
+        <v>270</v>
       </c>
       <c r="O20" t="n">
-        <v>48</v>
+        <v>270</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.9916591912703433</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3387,12 +3405,12 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3407,12 +3425,12 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -3449,12 +3467,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3479,23 +3497,26 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3529,7 +3550,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3549,7 +3570,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -3591,12 +3612,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3621,23 +3642,26 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.5536265131737159</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3671,7 +3695,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3691,7 +3715,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -3733,12 +3757,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3763,23 +3787,26 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.603207895901435</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3813,7 +3840,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3833,7 +3860,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -3875,12 +3902,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3905,26 +3932,26 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="O24" t="n">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2607696391859051</v>
+        <v>2.230174575626527</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3958,12 +3985,12 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3978,12 +4005,12 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -4020,12 +4047,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4050,23 +4077,26 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3130158239932889</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4100,7 +4130,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -4120,7 +4150,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -4162,12 +4192,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4192,23 +4222,26 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4242,7 +4275,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -4262,7 +4295,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -4304,12 +4337,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4334,23 +4367,26 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O27" t="n">
-        <v>32</v>
+        <v>22</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3075107688174575</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4384,7 +4420,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -4404,7 +4440,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -4446,12 +4482,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4476,23 +4512,26 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.002440393485997</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4526,7 +4565,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -4546,7 +4585,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -4588,12 +4627,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4618,23 +4657,26 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>314</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.153262911329214</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4668,12 +4710,12 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4688,12 +4730,12 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -4730,12 +4772,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4760,19 +4802,13 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
+          <t>2026-04</t>
+        </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -4810,7 +4846,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -4830,7 +4866,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -4872,12 +4908,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4902,26 +4938,26 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="O31" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2901521337420634</v>
+        <v>0.6228298273204304</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4955,35 +4991,7367 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>15</v>
+      </c>
+      <c r="O32" t="n">
+        <v>15</v>
+      </c>
+      <c r="R32" t="n">
+        <v>5.578302634074504</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>152</v>
+      </c>
+      <c r="O33" t="n">
+        <v>152</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.6483323085565</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>22</v>
+      </c>
+      <c r="O34" t="n">
+        <v>22</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.147724687975393</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>53</v>
+      </c>
+      <c r="O36" t="n">
+        <v>53</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.7408213976056932</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>29</v>
+      </c>
+      <c r="O37" t="n">
+        <v>29</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.9366253453402242</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>259</v>
+      </c>
+      <c r="O38" t="n">
+        <v>259</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.9512582612556257</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA31" t="inlineStr">
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB31" t="inlineStr">
+      <c r="BB38" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC31" t="inlineStr">
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>45</v>
+      </c>
+      <c r="O40" t="n">
+        <v>45</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.5190248561003586</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>19</v>
+      </c>
+      <c r="O41" t="n">
+        <v>19</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7.065850003161039</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>150</v>
+      </c>
+      <c r="O42" t="n">
+        <v>150</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.613485830812336</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>12</v>
+      </c>
+      <c r="O43" t="n">
+        <v>12</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.6260316479865778</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>10</v>
+      </c>
+      <c r="O45" t="n">
+        <v>10</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.1397776221897534</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>25</v>
+      </c>
+      <c r="O46" t="n">
+        <v>25</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.807435642534676</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>169</v>
+      </c>
+      <c r="O47" t="n">
+        <v>169</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.6207051974988445</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>24</v>
+      </c>
+      <c r="O49" t="n">
+        <v>24</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.276813256586858</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>12</v>
+      </c>
+      <c r="O50" t="n">
+        <v>12</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4.462642107259603</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>97</v>
+      </c>
+      <c r="O51" t="n">
+        <v>97</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.690054170591977</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>7</v>
+      </c>
+      <c r="O52" t="n">
+        <v>7</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.3651851279921704</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>10</v>
+      </c>
+      <c r="O54" t="n">
+        <v>10</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.1397776221897534</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>21</v>
+      </c>
+      <c r="O55" t="n">
+        <v>21</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.6782459397291279</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>99</v>
+      </c>
+      <c r="O56" t="n">
+        <v>99</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.3636083701324592</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>24</v>
+      </c>
+      <c r="O58" t="n">
+        <v>24</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.276813256586858</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>7</v>
+      </c>
+      <c r="O59" t="n">
+        <v>7</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2.603207895901435</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>49</v>
+      </c>
+      <c r="O60" t="n">
+        <v>49</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.8537387047320297</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>9</v>
+      </c>
+      <c r="O61" t="n">
+        <v>9</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.4695237359899334</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>5</v>
+      </c>
+      <c r="O63" t="n">
+        <v>5</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.06988881109487671</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>5</v>
+      </c>
+      <c r="O64" t="n">
+        <v>5</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.1614871285069352</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>67</v>
+      </c>
+      <c r="O65" t="n">
+        <v>67</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.246078391907826</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>20</v>
+      </c>
+      <c r="O67" t="n">
+        <v>20</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.2306777138223816</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>6</v>
+      </c>
+      <c r="O68" t="n">
+        <v>6</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2.231321053629801</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>32</v>
+      </c>
+      <c r="O69" t="n">
+        <v>32</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.5575436439066317</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>5</v>
+      </c>
+      <c r="O73" t="n">
+        <v>5</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.1614871285069352</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>75</v>
+      </c>
+      <c r="O74" t="n">
+        <v>75</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.2754608864639843</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>17</v>
+      </c>
+      <c r="O76" t="n">
+        <v>17</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.1960760567490244</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>50</v>
+      </c>
+      <c r="O78" t="n">
+        <v>50</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.8711619436041119</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
+      </c>
+      <c r="O82" t="n">
+        <v>5</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.1614871285069352</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -5105,7 +12473,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -5115,7 +12483,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
@@ -5167,7 +12535,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1637,6 +1667,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1782,6 +1817,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1927,6 +1967,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2075,6 +2120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2220,6 +2270,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2365,6 +2420,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2510,6 +2570,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2655,6 +2720,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2800,6 +2870,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2936,6 +3011,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3081,6 +3161,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3226,6 +3311,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3374,6 +3464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3519,6 +3614,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3664,6 +3764,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3809,6 +3914,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3954,6 +4064,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4099,6 +4214,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4244,6 +4364,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4389,6 +4514,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4534,6 +4664,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4679,6 +4814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4815,6 +4955,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4960,6 +5105,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5105,6 +5255,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5250,6 +5405,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5395,6 +5555,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5531,6 +5696,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5676,6 +5846,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5821,6 +5996,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5966,6 +6146,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6111,6 +6296,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6256,6 +6446,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6401,6 +6596,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6546,6 +6746,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6691,6 +6896,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6836,6 +7046,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6981,6 +7196,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7126,6 +7346,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7271,6 +7496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7416,6 +7646,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7561,6 +7796,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7706,6 +7946,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7851,6 +8096,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7996,6 +8246,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8141,6 +8396,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8286,6 +8546,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8431,6 +8696,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8576,6 +8846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8721,6 +8996,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8866,6 +9146,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9011,6 +9296,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9156,6 +9446,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9301,6 +9596,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9437,6 +9737,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9582,6 +9887,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9727,6 +10037,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9859,17 +10174,22 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O65" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R65" t="n">
-        <v>0.246078391907826</v>
+        <v>0.2497512037273457</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10017,6 +10337,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10162,6 +10487,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10307,6 +10637,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10452,6 +10787,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10588,6 +10928,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10733,6 +11078,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10869,6 +11219,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11014,6 +11369,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11146,17 +11506,22 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O74" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="R74" t="n">
-        <v>0.2754608864639843</v>
+        <v>0.2938249455615832</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -11304,6 +11669,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11449,6 +11819,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11585,6 +11960,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11730,6 +12110,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11866,6 +12251,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12011,6 +12401,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12147,6 +12542,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12290,6 +12690,11 @@
       <c r="S82" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12535,7 +12940,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3486</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -10174,13 +10174,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="O65" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="R65" t="n">
-        <v>0.2497512037273457</v>
+        <v>0.2717880746444645</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -11506,13 +11506,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O74" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R74" t="n">
-        <v>0.2938249455615832</v>
+        <v>0.297497757381103</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3492</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -10174,13 +10174,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O65" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R65" t="n">
-        <v>0.2717880746444645</v>
+        <v>0.2681152628249447</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -11506,13 +11506,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O74" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R74" t="n">
-        <v>0.297497757381103</v>
+        <v>0.2938249455615832</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3499</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -11506,13 +11506,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O74" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R74" t="n">
-        <v>0.2938249455615832</v>
+        <v>0.297497757381103</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3497</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.7970001648357945</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,22 +918,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1071,11 +1041,6 @@
       <c r="R4" t="n">
         <v>0.2306777138223816</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1088,22 +1053,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1221,11 +1176,6 @@
       <c r="R5" t="n">
         <v>6.322076318617771</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1238,22 +1188,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1371,11 +1311,6 @@
       <c r="R6" t="n">
         <v>0.8363154658599474</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1388,22 +1323,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1521,11 +1446,6 @@
       <c r="R7" t="n">
         <v>0.8868781679809853</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1538,22 +1458,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1662,11 +1572,6 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1679,22 +1584,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1812,11 +1707,6 @@
       <c r="R9" t="n">
         <v>0.8107102087005699</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1829,22 +1719,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1962,11 +1842,6 @@
       <c r="R10" t="n">
         <v>2.29311722479848</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1979,22 +1854,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2115,11 +1980,6 @@
       <c r="R11" t="n">
         <v>0.9439126376165859</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2132,22 +1992,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2265,11 +2115,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2282,22 +2127,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2415,11 +2250,6 @@
       <c r="R13" t="n">
         <v>0.3690843421158106</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2432,22 +2262,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2565,11 +2385,6 @@
       <c r="R14" t="n">
         <v>5.20641579180287</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2582,22 +2397,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2715,11 +2520,6 @@
       <c r="R15" t="n">
         <v>2.160481620138198</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2732,22 +2532,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2865,11 +2655,6 @@
       <c r="R16" t="n">
         <v>0.3130158239932889</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2882,22 +2667,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3006,11 +2781,6 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3023,22 +2793,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3156,11 +2916,6 @@
       <c r="R18" t="n">
         <v>0.4193328665692603</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3173,22 +2928,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3306,11 +3051,6 @@
       <c r="R19" t="n">
         <v>1.873250690680448</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3323,22 +3063,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3459,11 +3189,6 @@
       <c r="R20" t="n">
         <v>0.9916591912703433</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3476,22 +3201,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3609,11 +3324,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3626,22 +3336,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3759,11 +3459,6 @@
       <c r="R22" t="n">
         <v>0.5536265131737159</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3776,22 +3471,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3909,11 +3594,6 @@
       <c r="R23" t="n">
         <v>2.603207895901435</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3926,22 +3606,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4059,11 +3729,6 @@
       <c r="R24" t="n">
         <v>2.230174575626527</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4076,22 +3741,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4209,11 +3864,6 @@
       <c r="R25" t="n">
         <v>0.3130158239932889</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4226,22 +3876,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4359,11 +3999,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4376,22 +4011,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4509,11 +4134,6 @@
       <c r="R27" t="n">
         <v>0.3075107688174575</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4526,22 +4146,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4659,11 +4269,6 @@
       <c r="R28" t="n">
         <v>2.002440393485997</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4676,22 +4281,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4809,11 +4404,6 @@
       <c r="R29" t="n">
         <v>1.153262911329214</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4826,22 +4416,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4950,11 +4530,6 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4967,22 +4542,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5100,11 +4665,6 @@
       <c r="R31" t="n">
         <v>0.6228298273204304</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5117,22 +4677,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5250,11 +4800,6 @@
       <c r="R32" t="n">
         <v>5.578302634074504</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5267,22 +4812,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5400,11 +4935,6 @@
       <c r="R33" t="n">
         <v>2.6483323085565</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5417,22 +4947,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5550,11 +5070,6 @@
       <c r="R34" t="n">
         <v>1.147724687975393</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5567,22 +5082,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5691,11 +5196,6 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5708,22 +5208,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5841,11 +5331,6 @@
       <c r="R36" t="n">
         <v>0.7408213976056932</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5858,22 +5343,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5991,11 +5466,6 @@
       <c r="R37" t="n">
         <v>0.9366253453402242</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6008,22 +5478,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6141,11 +5601,6 @@
       <c r="R38" t="n">
         <v>0.9512582612556257</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6158,22 +5613,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6291,11 +5736,6 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6308,22 +5748,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6441,11 +5871,6 @@
       <c r="R40" t="n">
         <v>0.5190248561003586</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6458,22 +5883,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6591,11 +6006,6 @@
       <c r="R41" t="n">
         <v>7.065850003161039</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6608,22 +6018,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6741,11 +6141,6 @@
       <c r="R42" t="n">
         <v>2.613485830812336</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6758,22 +6153,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6891,11 +6276,6 @@
       <c r="R43" t="n">
         <v>0.6260316479865778</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6908,22 +6288,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7041,11 +6411,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7058,22 +6423,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7191,11 +6546,6 @@
       <c r="R45" t="n">
         <v>0.1397776221897534</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7208,22 +6558,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7341,11 +6681,6 @@
       <c r="R46" t="n">
         <v>0.807435642534676</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7358,22 +6693,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7491,11 +6816,6 @@
       <c r="R47" t="n">
         <v>0.6207051974988445</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7508,22 +6828,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7641,11 +6951,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7658,22 +6963,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7791,11 +7086,6 @@
       <c r="R49" t="n">
         <v>0.276813256586858</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7808,22 +7098,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7941,11 +7221,6 @@
       <c r="R50" t="n">
         <v>4.462642107259603</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7958,22 +7233,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8091,11 +7356,6 @@
       <c r="R51" t="n">
         <v>1.690054170591977</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8108,22 +7368,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8241,11 +7491,6 @@
       <c r="R52" t="n">
         <v>0.3651851279921704</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8258,22 +7503,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8391,11 +7626,6 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8408,22 +7638,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8541,11 +7761,6 @@
       <c r="R54" t="n">
         <v>0.1397776221897534</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8558,22 +7773,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8691,11 +7896,6 @@
       <c r="R55" t="n">
         <v>0.6782459397291279</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8708,22 +7908,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8841,11 +8031,6 @@
       <c r="R56" t="n">
         <v>0.3636083701324592</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8858,22 +8043,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8991,11 +8166,6 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9008,22 +8178,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9141,11 +8301,6 @@
       <c r="R58" t="n">
         <v>0.276813256586858</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9158,22 +8313,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9291,11 +8436,6 @@
       <c r="R59" t="n">
         <v>2.603207895901435</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9308,22 +8448,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9441,11 +8571,6 @@
       <c r="R60" t="n">
         <v>0.8537387047320297</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9458,22 +8583,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9591,11 +8706,6 @@
       <c r="R61" t="n">
         <v>0.4695237359899334</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9608,22 +8718,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9732,11 +8832,6 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9749,22 +8844,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9882,11 +8967,6 @@
       <c r="R63" t="n">
         <v>0.06988881109487671</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9899,22 +8979,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10032,11 +9102,6 @@
       <c r="R64" t="n">
         <v>0.1614871285069352</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10049,22 +9114,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10182,11 +9237,6 @@
       <c r="R65" t="n">
         <v>0.2681152628249447</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10199,22 +9249,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10332,11 +9372,6 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10349,22 +9384,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10482,11 +9507,6 @@
       <c r="R67" t="n">
         <v>0.2306777138223816</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10499,22 +9519,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10632,11 +9642,6 @@
       <c r="R68" t="n">
         <v>2.231321053629801</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10649,22 +9654,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10782,11 +9777,6 @@
       <c r="R69" t="n">
         <v>0.5575436439066317</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10799,22 +9789,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10923,11 +9903,6 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10940,22 +9915,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11073,11 +10038,6 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11090,22 +10050,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11214,11 +10164,6 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11231,22 +10176,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11364,11 +10299,6 @@
       <c r="R73" t="n">
         <v>0.1614871285069352</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11381,22 +10311,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11506,18 +10426,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O74" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R74" t="n">
-        <v>0.297497757381103</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0.2938249455615832</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -11531,22 +10446,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11664,11 +10569,6 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11681,22 +10581,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11814,11 +10704,6 @@
       <c r="R76" t="n">
         <v>0.1960760567490244</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11831,22 +10716,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11955,11 +10830,6 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11972,22 +10842,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12105,11 +10965,6 @@
       <c r="R78" t="n">
         <v>0.8711619436041119</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12122,22 +10977,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12246,11 +11091,6 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12263,22 +11103,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12396,11 +11226,6 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12413,22 +11238,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12537,11 +11352,6 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12554,22 +11364,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12687,11 +11487,6 @@
       <c r="R82" t="n">
         <v>0.1614871285069352</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12704,22 +11499,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12940,7 +11725,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3498</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -10426,13 +10426,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O74" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R74" t="n">
-        <v>0.2938249455615832</v>
+        <v>0.3011705692006228</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3497</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -10426,13 +10426,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O74" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3011705692006228</v>
+        <v>0.3048433810201426</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -11542,6 +11542,141 @@
         </is>
       </c>
       <c r="BC82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>61</v>
+      </c>
+      <c r="O83" t="n">
+        <v>61</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.2240415209907072</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -11580,7 +11715,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11798,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -11673,7 +11808,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -11725,7 +11860,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3499</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -10426,13 +10426,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O74" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3048433810201426</v>
+        <v>0.3085161928396624</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3561</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0.7970001648357945</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,13 +788,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,13 +938,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>all</t>
@@ -1041,6 +1071,11 @@
       <c r="R4" t="n">
         <v>0.2306777138223816</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1053,13 +1088,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
@@ -1176,6 +1221,11 @@
       <c r="R5" t="n">
         <v>6.322076318617771</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1188,13 +1238,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1311,6 +1371,11 @@
       <c r="R6" t="n">
         <v>0.8363154658599474</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1323,13 +1388,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
@@ -1446,6 +1521,11 @@
       <c r="R7" t="n">
         <v>0.8868781679809853</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1458,13 +1538,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>all</t>
@@ -1572,6 +1662,11 @@
           <t>2026-01</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1584,13 +1679,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>all</t>
@@ -1707,6 +1812,11 @@
       <c r="R9" t="n">
         <v>0.8107102087005699</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1719,13 +1829,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>all</t>
@@ -1842,6 +1962,11 @@
       <c r="R10" t="n">
         <v>2.29311722479848</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1854,13 +1979,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>all</t>
@@ -1980,6 +2115,11 @@
       <c r="R11" t="n">
         <v>0.9439126376165859</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1992,13 +2132,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>all</t>
@@ -2115,6 +2265,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2127,13 +2282,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>all</t>
@@ -2250,6 +2415,11 @@
       <c r="R13" t="n">
         <v>0.3690843421158106</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2262,13 +2432,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>all</t>
@@ -2385,6 +2565,11 @@
       <c r="R14" t="n">
         <v>5.20641579180287</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2397,13 +2582,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>all</t>
@@ -2520,6 +2715,11 @@
       <c r="R15" t="n">
         <v>2.160481620138198</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2532,13 +2732,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>all</t>
@@ -2655,6 +2865,11 @@
       <c r="R16" t="n">
         <v>0.3130158239932889</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2667,13 +2882,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -2781,6 +3006,11 @@
           <t>2026-02</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2793,13 +3023,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -2916,6 +3156,11 @@
       <c r="R18" t="n">
         <v>0.4193328665692603</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2928,13 +3173,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -3051,6 +3306,11 @@
       <c r="R19" t="n">
         <v>1.873250690680448</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3063,13 +3323,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -3189,6 +3459,11 @@
       <c r="R20" t="n">
         <v>0.9916591912703433</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3201,13 +3476,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3324,6 +3609,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3336,13 +3626,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3459,6 +3759,11 @@
       <c r="R22" t="n">
         <v>0.5536265131737159</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3471,13 +3776,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3594,6 +3909,11 @@
       <c r="R23" t="n">
         <v>2.603207895901435</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3606,13 +3926,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -3729,6 +4059,11 @@
       <c r="R24" t="n">
         <v>2.230174575626527</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3741,13 +4076,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -3864,6 +4209,11 @@
       <c r="R25" t="n">
         <v>0.3130158239932889</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3876,13 +4226,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -3999,6 +4359,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4011,13 +4376,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -4134,6 +4509,11 @@
       <c r="R27" t="n">
         <v>0.3075107688174575</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4146,13 +4526,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -4269,6 +4659,11 @@
       <c r="R28" t="n">
         <v>2.002440393485997</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4281,13 +4676,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4404,6 +4809,11 @@
       <c r="R29" t="n">
         <v>1.153262911329214</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4416,13 +4826,23 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>all</t>
@@ -4530,6 +4950,11 @@
           <t>2026-04</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4542,13 +4967,23 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>all</t>
@@ -4665,6 +5100,11 @@
       <c r="R31" t="n">
         <v>0.6228298273204304</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4677,13 +5117,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>all</t>
@@ -4800,6 +5250,11 @@
       <c r="R32" t="n">
         <v>5.578302634074504</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4812,13 +5267,23 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
@@ -4935,6 +5400,11 @@
       <c r="R33" t="n">
         <v>2.6483323085565</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4947,13 +5417,23 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
@@ -5070,6 +5550,11 @@
       <c r="R34" t="n">
         <v>1.147724687975393</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5082,13 +5567,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -5196,6 +5691,11 @@
           <t>2026-04</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5208,13 +5708,23 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -5331,6 +5841,11 @@
       <c r="R36" t="n">
         <v>0.7408213976056932</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5343,13 +5858,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -5466,6 +5991,11 @@
       <c r="R37" t="n">
         <v>0.9366253453402242</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5478,13 +6008,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -5601,6 +6141,11 @@
       <c r="R38" t="n">
         <v>0.9512582612556257</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5613,13 +6158,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -5736,6 +6291,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5748,13 +6308,23 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
@@ -5871,6 +6441,11 @@
       <c r="R40" t="n">
         <v>0.5190248561003586</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5883,13 +6458,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>all</t>
@@ -6006,6 +6591,11 @@
       <c r="R41" t="n">
         <v>7.065850003161039</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6018,13 +6608,23 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>all</t>
@@ -6141,6 +6741,11 @@
       <c r="R42" t="n">
         <v>2.613485830812336</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6153,13 +6758,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>all</t>
@@ -6276,6 +6891,11 @@
       <c r="R43" t="n">
         <v>0.6260316479865778</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6288,13 +6908,23 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>all</t>
@@ -6411,6 +7041,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6423,13 +7058,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>all</t>
@@ -6546,6 +7191,11 @@
       <c r="R45" t="n">
         <v>0.1397776221897534</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6558,13 +7208,23 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>all</t>
@@ -6681,6 +7341,11 @@
       <c r="R46" t="n">
         <v>0.807435642534676</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6693,13 +7358,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>all</t>
@@ -6816,6 +7491,11 @@
       <c r="R47" t="n">
         <v>0.6207051974988445</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6828,13 +7508,23 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>all</t>
@@ -6951,6 +7641,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6963,13 +7658,23 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>all</t>
@@ -7086,6 +7791,11 @@
       <c r="R49" t="n">
         <v>0.276813256586858</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7098,13 +7808,23 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>all</t>
@@ -7221,6 +7941,11 @@
       <c r="R50" t="n">
         <v>4.462642107259603</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7233,13 +7958,23 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>all</t>
@@ -7356,6 +8091,11 @@
       <c r="R51" t="n">
         <v>1.690054170591977</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7368,13 +8108,23 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>all</t>
@@ -7491,6 +8241,11 @@
       <c r="R52" t="n">
         <v>0.3651851279921704</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7503,13 +8258,23 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>all</t>
@@ -7626,6 +8391,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7638,13 +8408,23 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>all</t>
@@ -7761,6 +8541,11 @@
       <c r="R54" t="n">
         <v>0.1397776221897534</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7773,13 +8558,23 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
@@ -7896,6 +8691,11 @@
       <c r="R55" t="n">
         <v>0.6782459397291279</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7908,13 +8708,23 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>all</t>
@@ -8031,6 +8841,11 @@
       <c r="R56" t="n">
         <v>0.3636083701324592</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8043,13 +8858,23 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
@@ -8166,6 +8991,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8178,13 +9008,23 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
@@ -8301,6 +9141,11 @@
       <c r="R58" t="n">
         <v>0.276813256586858</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8313,13 +9158,23 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>all</t>
@@ -8436,6 +9291,11 @@
       <c r="R59" t="n">
         <v>2.603207895901435</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8448,13 +9308,23 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>all</t>
@@ -8571,6 +9441,11 @@
       <c r="R60" t="n">
         <v>0.8537387047320297</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8583,13 +9458,23 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>all</t>
@@ -8706,6 +9591,11 @@
       <c r="R61" t="n">
         <v>0.4695237359899334</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8718,13 +9608,23 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>all</t>
@@ -8832,6 +9732,11 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8844,13 +9749,23 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>all</t>
@@ -8967,6 +9882,11 @@
       <c r="R63" t="n">
         <v>0.06988881109487671</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8979,13 +9899,23 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV63" t="inlineStr">
         <is>
           <t>all</t>
@@ -9102,6 +10032,11 @@
       <c r="R64" t="n">
         <v>0.1614871285069352</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9114,13 +10049,23 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>all</t>
@@ -9237,6 +10182,11 @@
       <c r="R65" t="n">
         <v>0.2681152628249447</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9249,13 +10199,23 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>all</t>
@@ -9372,6 +10332,11 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9384,13 +10349,23 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>all</t>
@@ -9507,6 +10482,11 @@
       <c r="R67" t="n">
         <v>0.2306777138223816</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9519,13 +10499,23 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>all</t>
@@ -9642,6 +10632,11 @@
       <c r="R68" t="n">
         <v>2.231321053629801</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9654,13 +10649,23 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>all</t>
@@ -9777,6 +10782,11 @@
       <c r="R69" t="n">
         <v>0.5575436439066317</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9789,13 +10799,23 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>all</t>
@@ -9903,6 +10923,11 @@
           <t>2026-08</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9915,13 +10940,23 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>all</t>
@@ -10038,6 +11073,11 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10050,13 +11090,23 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>all</t>
@@ -10164,6 +11214,11 @@
           <t>2026-08</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10176,13 +11231,23 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>all</t>
@@ -10299,6 +11364,11 @@
       <c r="R73" t="n">
         <v>0.1614871285069352</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10311,13 +11381,23 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>all</t>
@@ -10426,13 +11506,18 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O74" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3085161928396624</v>
+        <v>0.3121890046591821</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -10446,13 +11531,23 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV74" t="inlineStr">
         <is>
           <t>all</t>
@@ -10569,6 +11664,11 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10581,13 +11681,23 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
       </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>all</t>
@@ -10704,6 +11814,11 @@
       <c r="R76" t="n">
         <v>0.1960760567490244</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10716,13 +11831,23 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
@@ -10830,6 +11955,11 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10842,13 +11972,23 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>all</t>
@@ -10965,6 +12105,11 @@
       <c r="R78" t="n">
         <v>0.8711619436041119</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10977,13 +12122,23 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV78" t="inlineStr">
         <is>
           <t>all</t>
@@ -11091,6 +12246,11 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11103,13 +12263,23 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>all</t>
@@ -11226,6 +12396,11 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11238,13 +12413,23 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>all</t>
@@ -11352,6 +12537,11 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11364,13 +12554,23 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV81" t="inlineStr">
         <is>
           <t>all</t>
@@ -11487,6 +12687,11 @@
       <c r="R82" t="n">
         <v>0.1614871285069352</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11499,13 +12704,23 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>all</t>
@@ -11622,6 +12837,11 @@
       <c r="R83" t="n">
         <v>0.2240415209907072</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11634,12 +12854,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -11860,7 +13090,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3562</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="16">
